--- a/docs/variable_typing.xlsx
+++ b/docs/variable_typing.xlsx
@@ -31,7 +31,7 @@
       <color rgb="00FFFFFF"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="9">
     <fill>
       <patternFill/>
     </fill>
@@ -65,6 +65,11 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="00F3EDF7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="00FFF6DD"/>
       </patternFill>
     </fill>
@@ -81,7 +86,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
@@ -102,6 +107,9 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -470,7 +478,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G32"/>
+  <dimension ref="A1:G34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -1491,28 +1499,28 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>final_result</t>
+          <t>date_unregistration</t>
         </is>
       </c>
       <c r="B31" s="7" t="inlineStr">
         <is>
-          <t>Target (raw)</t>
+          <t>Temporal</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>Nominal (raw)</t>
+          <t>Numeric (continuous)</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>Danh định (gốc)</t>
+          <t>Định lượng (liên tục)</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr"/>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>Mapped to at_risk</t>
+          <t>Not a feature (Withdrawn analysis)</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -1524,31 +1532,97 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>at_risk</t>
+          <t>module_presentation_length</t>
         </is>
       </c>
       <c r="B32" s="7" t="inlineStr">
         <is>
-          <t>Target</t>
+          <t>Temporal</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>Binary (target)</t>
+          <t>Numeric (discrete)</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>Nhị phân (mục tiêu)</t>
+          <t>Định lượng (rời rạc)</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr"/>
       <c r="F32" s="2" t="inlineStr">
         <is>
+          <t>Checkpoint-day conversion</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>Original</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>final_result</t>
+        </is>
+      </c>
+      <c r="B33" s="8" t="inlineStr">
+        <is>
+          <t>Target (raw)</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>Nominal (raw)</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>Danh định (gốc)</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr"/>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>Mapped to at_risk</t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="inlineStr">
+        <is>
+          <t>Original</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>at_risk</t>
+        </is>
+      </c>
+      <c r="B34" s="8" t="inlineStr">
+        <is>
+          <t>Target</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>Binary (target)</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>Nhị phân (mục tiêu)</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr"/>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
           <t>None (target)</t>
         </is>
       </c>
-      <c r="G32" s="2" t="inlineStr">
+      <c r="G34" s="2" t="inlineStr">
         <is>
           <t>Derived</t>
         </is>
@@ -1574,17 +1648,17 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="8" t="inlineStr">
+      <c r="A1" s="9" t="inlineStr">
         <is>
           <t>Column</t>
         </is>
       </c>
-      <c r="B1" s="8" t="inlineStr">
+      <c r="B1" s="9" t="inlineStr">
         <is>
           <t>Meaning (EN)</t>
         </is>
       </c>
-      <c r="C1" s="8" t="inlineStr">
+      <c r="C1" s="9" t="inlineStr">
         <is>
           <t>Ý nghĩa (VI)</t>
         </is>
